--- a/data/nzd0110/nzd0110.xlsx
+++ b/data/nzd0110/nzd0110.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K336"/>
+  <dimension ref="A1:K338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13542,6 +13542,84 @@
         <v>393.21</v>
       </c>
       <c r="K336" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>388.66</v>
+      </c>
+      <c r="C337" t="n">
+        <v>382.53</v>
+      </c>
+      <c r="D337" t="n">
+        <v>385.63</v>
+      </c>
+      <c r="E337" t="n">
+        <v>386.04</v>
+      </c>
+      <c r="F337" t="n">
+        <v>385.88</v>
+      </c>
+      <c r="G337" t="n">
+        <v>385.79</v>
+      </c>
+      <c r="H337" t="n">
+        <v>385.3</v>
+      </c>
+      <c r="I337" t="n">
+        <v>391.28</v>
+      </c>
+      <c r="J337" t="n">
+        <v>394.08</v>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>389.75</v>
+      </c>
+      <c r="C338" t="n">
+        <v>382.61</v>
+      </c>
+      <c r="D338" t="n">
+        <v>385.25</v>
+      </c>
+      <c r="E338" t="n">
+        <v>385.89</v>
+      </c>
+      <c r="F338" t="n">
+        <v>386.01</v>
+      </c>
+      <c r="G338" t="n">
+        <v>386.79</v>
+      </c>
+      <c r="H338" t="n">
+        <v>385.12</v>
+      </c>
+      <c r="I338" t="n">
+        <v>390.65</v>
+      </c>
+      <c r="J338" t="n">
+        <v>394.43</v>
+      </c>
+      <c r="K338" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13558,7 +13636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B458"/>
+  <dimension ref="A1:B460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18141,6 +18219,26 @@
       </c>
       <c r="B458" t="n">
         <v>-0.74</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>-0.24</v>
       </c>
     </row>
   </sheetData>
@@ -18309,28 +18407,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09185010189584689</v>
+        <v>0.09147941285563373</v>
       </c>
       <c r="J2" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K2" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02410003232762226</v>
+        <v>0.02421564597639425</v>
       </c>
       <c r="M2" t="n">
-        <v>3.587614692345062</v>
+        <v>3.569492796533017</v>
       </c>
       <c r="N2" t="n">
-        <v>19.49605639315442</v>
+        <v>19.38270841131211</v>
       </c>
       <c r="O2" t="n">
-        <v>4.415433885039433</v>
+        <v>4.402579745025877</v>
       </c>
       <c r="P2" t="n">
-        <v>387.0604848102794</v>
+        <v>387.0643948727638</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18387,28 +18485,28 @@
         <v>0.1068</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.01654873938422049</v>
+        <v>-0.01857295963787287</v>
       </c>
       <c r="J3" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K3" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009036190219676721</v>
+        <v>0.001151738594383334</v>
       </c>
       <c r="M3" t="n">
-        <v>3.346646298887238</v>
+        <v>3.335928998581146</v>
       </c>
       <c r="N3" t="n">
-        <v>17.28031533886094</v>
+        <v>17.19561692892494</v>
       </c>
       <c r="O3" t="n">
-        <v>4.156959867362318</v>
+        <v>4.146759810855331</v>
       </c>
       <c r="P3" t="n">
-        <v>384.7663567524747</v>
+        <v>384.7877444780531</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18465,28 +18563,28 @@
         <v>0.0603</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.05596357269430086</v>
+        <v>-0.05882134601833647</v>
       </c>
       <c r="J4" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K4" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009695472368147828</v>
+        <v>0.01081870705974941</v>
       </c>
       <c r="M4" t="n">
-        <v>3.24892943396967</v>
+        <v>3.241834934975052</v>
       </c>
       <c r="N4" t="n">
-        <v>18.25620334794121</v>
+        <v>18.18362153463122</v>
       </c>
       <c r="O4" t="n">
-        <v>4.272727857931184</v>
+        <v>4.264225783730409</v>
       </c>
       <c r="P4" t="n">
-        <v>389.4156470087644</v>
+        <v>389.445845071844</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18543,28 +18641,28 @@
         <v>0.077</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01108696783067474</v>
+        <v>-0.01210976954931792</v>
       </c>
       <c r="J5" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K5" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0004481208312629992</v>
+        <v>0.0005414618119221615</v>
       </c>
       <c r="M5" t="n">
-        <v>3.004552381877947</v>
+        <v>2.991786755727416</v>
       </c>
       <c r="N5" t="n">
-        <v>15.64716243019394</v>
+        <v>15.55889110351179</v>
       </c>
       <c r="O5" t="n">
-        <v>3.95564943216584</v>
+        <v>3.944476023949415</v>
       </c>
       <c r="P5" t="n">
-        <v>387.1475567956645</v>
+        <v>387.1583648638933</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18621,28 +18719,28 @@
         <v>0.0769</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1541594150720383</v>
+        <v>-0.1511204353946841</v>
       </c>
       <c r="J6" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K6" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09776689957291729</v>
+        <v>0.09515794463853688</v>
       </c>
       <c r="M6" t="n">
-        <v>2.688731600084711</v>
+        <v>2.688586005249178</v>
       </c>
       <c r="N6" t="n">
-        <v>12.51603675669591</v>
+        <v>12.48199633982048</v>
       </c>
       <c r="O6" t="n">
-        <v>3.537801118872556</v>
+        <v>3.532986886448983</v>
       </c>
       <c r="P6" t="n">
-        <v>387.4603307321024</v>
+        <v>387.4282195001592</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18699,28 +18797,28 @@
         <v>0.0553</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.00218377586743275</v>
+        <v>-0.003014334564058848</v>
       </c>
       <c r="J7" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K7" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L7" t="n">
-        <v>1.523983267903706e-05</v>
+        <v>2.941209121354316e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.997471262520221</v>
+        <v>2.983191552775115</v>
       </c>
       <c r="N7" t="n">
-        <v>17.8578477620004</v>
+        <v>17.75636905392455</v>
       </c>
       <c r="O7" t="n">
-        <v>4.225854678287033</v>
+        <v>4.213830686433018</v>
       </c>
       <c r="P7" t="n">
-        <v>387.0700341693791</v>
+        <v>387.0788038177008</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18777,28 +18875,28 @@
         <v>0.0612</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2412503855907938</v>
+        <v>-0.2403415847609634</v>
       </c>
       <c r="J8" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K8" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1816206983478411</v>
+        <v>0.1824126854217045</v>
       </c>
       <c r="M8" t="n">
-        <v>3.014821313153751</v>
+        <v>3.000437172801475</v>
       </c>
       <c r="N8" t="n">
-        <v>15.01146194198648</v>
+        <v>14.92576104138118</v>
       </c>
       <c r="O8" t="n">
-        <v>3.874462793986603</v>
+        <v>3.863387249730628</v>
       </c>
       <c r="P8" t="n">
-        <v>390.9155190309256</v>
+        <v>390.9059311051473</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18855,28 +18953,28 @@
         <v>0.0616</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2948233055147932</v>
+        <v>-0.293665259256809</v>
       </c>
       <c r="J9" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K9" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3292190300102824</v>
+        <v>0.3302362152851889</v>
       </c>
       <c r="M9" t="n">
-        <v>2.487771421373857</v>
+        <v>2.478603508194726</v>
       </c>
       <c r="N9" t="n">
-        <v>10.13717832275514</v>
+        <v>10.08327572204393</v>
       </c>
       <c r="O9" t="n">
-        <v>3.183893579056174</v>
+        <v>3.175417409104498</v>
       </c>
       <c r="P9" t="n">
-        <v>397.8940030962414</v>
+        <v>397.8817880925523</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18933,28 +19031,28 @@
         <v>0.0522</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3848633481567118</v>
+        <v>-0.3846052624084834</v>
       </c>
       <c r="J10" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K10" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L10" t="n">
-        <v>0.365604882544857</v>
+        <v>0.3683314174301934</v>
       </c>
       <c r="M10" t="n">
-        <v>2.654074573501898</v>
+        <v>2.639378087142283</v>
       </c>
       <c r="N10" t="n">
-        <v>14.71155616270498</v>
+        <v>14.62448201914431</v>
       </c>
       <c r="O10" t="n">
-        <v>3.835564647181036</v>
+        <v>3.824196911659272</v>
       </c>
       <c r="P10" t="n">
-        <v>404.3847449985378</v>
+        <v>404.382019576384</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18992,7 +19090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K336"/>
+  <dimension ref="A1:K338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38135,6 +38233,120 @@
         </is>
       </c>
     </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>-36.04660169922374,174.54636799678985</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>-36.046967749337774,174.547142319477</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>-36.0472264695636,174.54795819079277</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>-36.047431026439085,174.54879577805343</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>-36.04760324772801,174.54965577965902</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>-36.04775636871899,174.55052257454895</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>-36.04787430668475,174.5513945792339</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>-36.04790123086143,174.5522546410184</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>-36.04782087972939,174.5531155978336</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>-36.046592822900394,174.54637318328392</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>-36.046967091762724,174.54714268388278</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>-36.04722969228957,174.54795676211847</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>-36.047432333183984,174.54879535064572</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>-36.04760210345319,174.54965609046752</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>-36.047747494821586,174.55052452187056</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>-36.047875916259734,174.55139432787973</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>-36.04790690934801,174.55225459116423</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>-36.04781773735704,174.55311525343495</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0110/nzd0110.xlsx
+++ b/data/nzd0110/nzd0110.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K338"/>
+  <dimension ref="A1:K339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13620,6 +13620,45 @@
         <v>394.43</v>
       </c>
       <c r="K338" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>390.7</v>
+      </c>
+      <c r="C339" t="n">
+        <v>383.23</v>
+      </c>
+      <c r="D339" t="n">
+        <v>387.72</v>
+      </c>
+      <c r="E339" t="n">
+        <v>387.54</v>
+      </c>
+      <c r="F339" t="n">
+        <v>387.03</v>
+      </c>
+      <c r="G339" t="n">
+        <v>388.51</v>
+      </c>
+      <c r="H339" t="n">
+        <v>386.25</v>
+      </c>
+      <c r="I339" t="n">
+        <v>391.13</v>
+      </c>
+      <c r="J339" t="n">
+        <v>395.66</v>
+      </c>
+      <c r="K339" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13636,7 +13675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B460"/>
+  <dimension ref="A1:B461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18239,6 +18278,16 @@
       </c>
       <c r="B460" t="n">
         <v>-0.24</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>
@@ -18407,28 +18456,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09147941285563373</v>
+        <v>0.09215525336529502</v>
       </c>
       <c r="J2" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K2" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02421564597639425</v>
+        <v>0.02471675537385531</v>
       </c>
       <c r="M2" t="n">
-        <v>3.569492796533017</v>
+        <v>3.562480845013114</v>
       </c>
       <c r="N2" t="n">
-        <v>19.38270841131211</v>
+        <v>19.32941321124557</v>
       </c>
       <c r="O2" t="n">
-        <v>4.402579745025877</v>
+        <v>4.396522854625638</v>
       </c>
       <c r="P2" t="n">
-        <v>387.0643948727638</v>
+        <v>387.0572407314829</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18485,28 +18534,28 @@
         <v>0.1068</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.01857295963787287</v>
+        <v>-0.0191821389466617</v>
       </c>
       <c r="J3" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K3" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001151738594383334</v>
+        <v>0.001236180051959357</v>
       </c>
       <c r="M3" t="n">
-        <v>3.335928998581146</v>
+        <v>3.328791437717887</v>
       </c>
       <c r="N3" t="n">
-        <v>17.19561692892494</v>
+        <v>17.14803285857149</v>
       </c>
       <c r="O3" t="n">
-        <v>4.146759810855331</v>
+        <v>4.14101833593761</v>
       </c>
       <c r="P3" t="n">
-        <v>384.7877444780531</v>
+        <v>384.7941929740786</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18563,28 +18612,28 @@
         <v>0.0603</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.05882134601833647</v>
+        <v>-0.05890059092314398</v>
       </c>
       <c r="J4" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K4" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01081870705974941</v>
+        <v>0.0109173228326428</v>
       </c>
       <c r="M4" t="n">
-        <v>3.241834934975052</v>
+        <v>3.232579359850641</v>
       </c>
       <c r="N4" t="n">
-        <v>18.18362153463122</v>
+        <v>18.1298795203245</v>
       </c>
       <c r="O4" t="n">
-        <v>4.264225783730409</v>
+        <v>4.257919623516218</v>
       </c>
       <c r="P4" t="n">
-        <v>389.445845071844</v>
+        <v>389.4466839224851</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18641,28 +18690,28 @@
         <v>0.077</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01210976954931792</v>
+        <v>-0.01170535663777561</v>
       </c>
       <c r="J5" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K5" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005414618119221615</v>
+        <v>0.0005091606718081731</v>
       </c>
       <c r="M5" t="n">
-        <v>2.991786755727416</v>
+        <v>2.985068761350438</v>
       </c>
       <c r="N5" t="n">
-        <v>15.55889110351179</v>
+        <v>15.51430907622424</v>
       </c>
       <c r="O5" t="n">
-        <v>3.944476023949415</v>
+        <v>3.938820772290132</v>
       </c>
       <c r="P5" t="n">
-        <v>387.1583648638933</v>
+        <v>387.1540839321296</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18719,28 +18768,28 @@
         <v>0.0769</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1511204353946841</v>
+        <v>-0.1490110608104518</v>
       </c>
       <c r="J6" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K6" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09515794463853688</v>
+        <v>0.09304441900659577</v>
       </c>
       <c r="M6" t="n">
-        <v>2.688586005249178</v>
+        <v>2.691681560932813</v>
       </c>
       <c r="N6" t="n">
-        <v>12.48199633982048</v>
+        <v>12.48452069605682</v>
       </c>
       <c r="O6" t="n">
-        <v>3.532986886448983</v>
+        <v>3.533344123639363</v>
       </c>
       <c r="P6" t="n">
-        <v>387.4282195001592</v>
+        <v>387.4058906169772</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18797,28 +18846,28 @@
         <v>0.0553</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.003014334564058848</v>
+        <v>-0.002146924744864697</v>
       </c>
       <c r="J7" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K7" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L7" t="n">
-        <v>2.941209121354316e-05</v>
+        <v>1.501188754871041e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.983191552775115</v>
+        <v>2.979574867217844</v>
       </c>
       <c r="N7" t="n">
-        <v>17.75636905392455</v>
+        <v>17.71050694116742</v>
       </c>
       <c r="O7" t="n">
-        <v>4.213830686433018</v>
+        <v>4.208385312820989</v>
       </c>
       <c r="P7" t="n">
-        <v>387.0788038177008</v>
+        <v>387.0696218105464</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18875,28 +18924,28 @@
         <v>0.0612</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2403415847609634</v>
+        <v>-0.2392953721591922</v>
       </c>
       <c r="J8" t="n">
+        <v>338</v>
+      </c>
+      <c r="K8" t="n">
         <v>337</v>
       </c>
-      <c r="K8" t="n">
-        <v>336</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.1824126854217045</v>
+        <v>0.1819812317742383</v>
       </c>
       <c r="M8" t="n">
-        <v>3.000437172801475</v>
+        <v>2.995601747745462</v>
       </c>
       <c r="N8" t="n">
-        <v>14.92576104138118</v>
+        <v>14.89120634261102</v>
       </c>
       <c r="O8" t="n">
-        <v>3.863387249730628</v>
+        <v>3.85891258551046</v>
       </c>
       <c r="P8" t="n">
-        <v>390.9059311051473</v>
+        <v>390.8948719193608</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18953,28 +19002,28 @@
         <v>0.0616</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.293665259256809</v>
+        <v>-0.2929996270755271</v>
       </c>
       <c r="J9" t="n">
+        <v>338</v>
+      </c>
+      <c r="K9" t="n">
         <v>337</v>
       </c>
-      <c r="K9" t="n">
-        <v>336</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.3302362152851889</v>
+        <v>0.3305798135531118</v>
       </c>
       <c r="M9" t="n">
-        <v>2.478603508194726</v>
+        <v>2.474466917798494</v>
       </c>
       <c r="N9" t="n">
-        <v>10.08327572204393</v>
+        <v>10.05729580293652</v>
       </c>
       <c r="O9" t="n">
-        <v>3.175417409104498</v>
+        <v>3.171323982650861</v>
       </c>
       <c r="P9" t="n">
-        <v>397.8817880925523</v>
+        <v>397.8747519032101</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -19031,28 +19080,28 @@
         <v>0.0522</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3846052624084834</v>
+        <v>-0.3836643651180588</v>
       </c>
       <c r="J10" t="n">
+        <v>338</v>
+      </c>
+      <c r="K10" t="n">
         <v>337</v>
       </c>
-      <c r="K10" t="n">
-        <v>336</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.3683314174301934</v>
+        <v>0.3685745217779202</v>
       </c>
       <c r="M10" t="n">
-        <v>2.639378087142283</v>
+        <v>2.635541112437761</v>
       </c>
       <c r="N10" t="n">
-        <v>14.62448201914431</v>
+        <v>14.58895997783436</v>
       </c>
       <c r="O10" t="n">
-        <v>3.824196911659272</v>
+        <v>3.819549708779081</v>
       </c>
       <c r="P10" t="n">
-        <v>404.382019576384</v>
+        <v>404.3720736457737</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -19090,7 +19139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K338"/>
+  <dimension ref="A1:K339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38347,6 +38396,63 @@
         </is>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>-36.0465850866551,174.54637770362183</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>-36.04696199555604,174.5471455080274</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>-36.04720874457045,174.54796604849943</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>-36.04741795898994,174.54880005212993</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>-36.04759312529668,174.54965852911835</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>-36.04773223171797,174.55052787126277</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>-36.047865811705655,174.551395905825</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>-36.04790258288203,174.55225462914834</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>-36.04780669416275,174.5531140431199</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0110/nzd0110.xlsx
+++ b/data/nzd0110/nzd0110.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K339"/>
+  <dimension ref="A1:K341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13661,6 +13661,84 @@
       <c r="K339" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>391.34</v>
+      </c>
+      <c r="C340" t="n">
+        <v>384.53</v>
+      </c>
+      <c r="D340" t="n">
+        <v>388.23</v>
+      </c>
+      <c r="E340" t="n">
+        <v>387.46</v>
+      </c>
+      <c r="F340" t="n">
+        <v>386.99</v>
+      </c>
+      <c r="G340" t="n">
+        <v>388.4</v>
+      </c>
+      <c r="H340" t="n">
+        <v>386.55</v>
+      </c>
+      <c r="I340" t="n">
+        <v>391.21</v>
+      </c>
+      <c r="J340" t="n">
+        <v>395.87</v>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>389.2</v>
+      </c>
+      <c r="C341" t="n">
+        <v>383.25</v>
+      </c>
+      <c r="D341" t="n">
+        <v>387.41</v>
+      </c>
+      <c r="E341" t="n">
+        <v>388.77</v>
+      </c>
+      <c r="F341" t="n">
+        <v>386.99</v>
+      </c>
+      <c r="G341" t="n">
+        <v>388.98</v>
+      </c>
+      <c r="H341" t="n">
+        <v>386.49</v>
+      </c>
+      <c r="I341" t="n">
+        <v>392.1</v>
+      </c>
+      <c r="J341" t="n">
+        <v>395.57</v>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13675,7 +13753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B461"/>
+  <dimension ref="A1:B463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18288,6 +18366,26 @@
       </c>
       <c r="B461" t="n">
         <v>0.54</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>0.86</v>
       </c>
     </row>
   </sheetData>
@@ -18456,28 +18554,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09215525336529502</v>
+        <v>0.09297959173457283</v>
       </c>
       <c r="J2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02471675537385531</v>
+        <v>0.02545669044108867</v>
       </c>
       <c r="M2" t="n">
-        <v>3.562480845013114</v>
+        <v>3.54791348910066</v>
       </c>
       <c r="N2" t="n">
-        <v>19.32941321124557</v>
+        <v>19.22549108657353</v>
       </c>
       <c r="O2" t="n">
-        <v>4.396522854625638</v>
+        <v>4.384688254206168</v>
       </c>
       <c r="P2" t="n">
-        <v>387.0572407314829</v>
+        <v>387.0484838178951</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18534,28 +18632,28 @@
         <v>0.1068</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0191821389466617</v>
+        <v>-0.01962204869710607</v>
       </c>
       <c r="J3" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K3" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001236180051959357</v>
+        <v>0.001310045543967742</v>
       </c>
       <c r="M3" t="n">
-        <v>3.328791437717887</v>
+        <v>3.312704609467701</v>
       </c>
       <c r="N3" t="n">
-        <v>17.14803285857149</v>
+        <v>17.05045429823241</v>
       </c>
       <c r="O3" t="n">
-        <v>4.14101833593761</v>
+        <v>4.129219574959948</v>
       </c>
       <c r="P3" t="n">
-        <v>384.7941929740786</v>
+        <v>384.7988730780249</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18612,28 +18710,28 @@
         <v>0.0603</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.05890059092314398</v>
+        <v>-0.05894365383334359</v>
       </c>
       <c r="J4" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K4" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0109173228326428</v>
+        <v>0.0110734901045817</v>
       </c>
       <c r="M4" t="n">
-        <v>3.232579359850641</v>
+        <v>3.215929961176689</v>
       </c>
       <c r="N4" t="n">
-        <v>18.1298795203245</v>
+        <v>18.02422390908055</v>
       </c>
       <c r="O4" t="n">
-        <v>4.257919623516218</v>
+        <v>4.245494542344926</v>
       </c>
       <c r="P4" t="n">
-        <v>389.4466839224851</v>
+        <v>389.4471440409425</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18690,28 +18788,28 @@
         <v>0.077</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01170535663777561</v>
+        <v>-0.01025011454929787</v>
       </c>
       <c r="J5" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K5" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005091606718081731</v>
+        <v>0.0003952590442040105</v>
       </c>
       <c r="M5" t="n">
-        <v>2.985068761350438</v>
+        <v>2.975071120577677</v>
       </c>
       <c r="N5" t="n">
-        <v>15.51430907622424</v>
+        <v>15.43500939601831</v>
       </c>
       <c r="O5" t="n">
-        <v>3.938820772290132</v>
+        <v>3.928741451917944</v>
       </c>
       <c r="P5" t="n">
-        <v>387.1540839321296</v>
+        <v>387.1386103583055</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18768,28 +18866,28 @@
         <v>0.0769</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1490110608104518</v>
+        <v>-0.1449012051396716</v>
       </c>
       <c r="J6" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K6" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09304441900659577</v>
+        <v>0.08898886291174946</v>
       </c>
       <c r="M6" t="n">
-        <v>2.691681560932813</v>
+        <v>2.69745045552929</v>
       </c>
       <c r="N6" t="n">
-        <v>12.48452069605682</v>
+        <v>12.48633530498985</v>
       </c>
       <c r="O6" t="n">
-        <v>3.533344123639363</v>
+        <v>3.53360089780805</v>
       </c>
       <c r="P6" t="n">
-        <v>387.4058906169772</v>
+        <v>387.3622011809375</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18846,28 +18944,28 @@
         <v>0.0553</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.002146924744864697</v>
+        <v>-0.0002344128702507103</v>
       </c>
       <c r="J7" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K7" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L7" t="n">
-        <v>1.501188754871041e-05</v>
+        <v>1.811268842688563e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>2.979574867217844</v>
+        <v>2.973367403044113</v>
       </c>
       <c r="N7" t="n">
-        <v>17.71050694116742</v>
+        <v>17.62312336499921</v>
       </c>
       <c r="O7" t="n">
-        <v>4.208385312820989</v>
+        <v>4.197990396010836</v>
       </c>
       <c r="P7" t="n">
-        <v>387.0696218105464</v>
+        <v>387.049289356626</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18924,28 +19022,28 @@
         <v>0.0612</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2392953721591922</v>
+        <v>-0.2369090924354688</v>
       </c>
       <c r="J8" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K8" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1819812317742383</v>
+        <v>0.1806734553386048</v>
       </c>
       <c r="M8" t="n">
-        <v>2.995601747745462</v>
+        <v>2.987055538132322</v>
       </c>
       <c r="N8" t="n">
-        <v>14.89120634261102</v>
+        <v>14.82880526219865</v>
       </c>
       <c r="O8" t="n">
-        <v>3.85891258551046</v>
+        <v>3.850818778155972</v>
       </c>
       <c r="P8" t="n">
-        <v>390.8948719193608</v>
+        <v>390.8695400812076</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -19002,28 +19100,28 @@
         <v>0.0616</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2929996270755271</v>
+        <v>-0.2910619129456765</v>
       </c>
       <c r="J9" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K9" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3305798135531118</v>
+        <v>0.3301129450390303</v>
       </c>
       <c r="M9" t="n">
-        <v>2.474466917798494</v>
+        <v>2.469182616577301</v>
       </c>
       <c r="N9" t="n">
-        <v>10.05729580293652</v>
+        <v>10.01589626568699</v>
       </c>
       <c r="O9" t="n">
-        <v>3.171323982650861</v>
+        <v>3.164790082404675</v>
       </c>
       <c r="P9" t="n">
-        <v>397.8747519032101</v>
+        <v>397.8541791908355</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -19080,28 +19178,28 @@
         <v>0.0522</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3836643651180588</v>
+        <v>-0.3817056050075315</v>
       </c>
       <c r="J10" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K10" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3685745217779202</v>
+        <v>0.3689294961266054</v>
       </c>
       <c r="M10" t="n">
-        <v>2.635541112437761</v>
+        <v>2.628353813883878</v>
       </c>
       <c r="N10" t="n">
-        <v>14.58895997783436</v>
+        <v>14.52016683522488</v>
       </c>
       <c r="O10" t="n">
-        <v>3.819549708779081</v>
+        <v>3.810533668034555</v>
       </c>
       <c r="P10" t="n">
-        <v>404.3720736457737</v>
+        <v>404.3512809166418</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -19139,7 +19237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K339"/>
+  <dimension ref="A1:K341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38453,6 +38551,120 @@
         </is>
       </c>
     </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>-36.04657987486872,174.54638074890164</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>-36.04695130996117,174.54715142961984</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>-36.04720441933282,174.54796796592973</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>-36.04741865592056,174.5487998241792</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>-36.04759347738126,174.549658433485</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>-36.0477332078467,174.5505276570575</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>-36.04786312908068,174.55139632474848</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>-36.04790186180437,174.55225463547904</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>-36.04780480873933,174.55311383648078</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>-36.046597301779165,174.54637056624577</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>-36.04696183116228,174.54714559912884</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>-36.04721137363645,174.5479648830025</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>-36.04740724368154,174.54880355687166</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>-36.04759347738126,174.549658433485</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>-36.04772806098615,174.55052878650346</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>-36.047863665605675,174.55139624096378</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>-36.0478938398154,174.55225470590796</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>-36.04780750220136,174.55311413167954</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
